--- a/artfynd/A 18680-2024 artfynd.xlsx
+++ b/artfynd/A 18680-2024 artfynd.xlsx
@@ -1029,7 +1029,7 @@
         <v>117766659</v>
       </c>
       <c r="B5" t="n">
-        <v>96797</v>
+        <v>96799</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 18680-2024 artfynd.xlsx
+++ b/artfynd/A 18680-2024 artfynd.xlsx
@@ -1137,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152794</v>
+        <v>121152787</v>
       </c>
       <c r="B6" t="n">
-        <v>97031</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,30 +1149,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542863</v>
+        <v>542650</v>
       </c>
       <c r="R6" t="n">
-        <v>6853500</v>
+        <v>6853570</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152787</v>
+        <v>121152794</v>
       </c>
       <c r="B7" t="n">
-        <v>98071</v>
+        <v>97041</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,30 +1260,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542650</v>
+        <v>542863</v>
       </c>
       <c r="R7" t="n">
-        <v>6853570</v>
+        <v>6853500</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 18680-2024 artfynd.xlsx
+++ b/artfynd/A 18680-2024 artfynd.xlsx
@@ -1137,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152787</v>
+        <v>121152794</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>97054</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,30 +1149,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542650</v>
+        <v>542863</v>
       </c>
       <c r="R6" t="n">
-        <v>6853570</v>
+        <v>6853500</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152794</v>
+        <v>121152787</v>
       </c>
       <c r="B7" t="n">
-        <v>97041</v>
+        <v>98094</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,30 +1260,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542863</v>
+        <v>542650</v>
       </c>
       <c r="R7" t="n">
-        <v>6853500</v>
+        <v>6853570</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>

--- a/artfynd/A 18680-2024 artfynd.xlsx
+++ b/artfynd/A 18680-2024 artfynd.xlsx
@@ -1140,7 +1140,7 @@
         <v>121152794</v>
       </c>
       <c r="B6" t="n">
-        <v>97054</v>
+        <v>97055</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>121152787</v>
       </c>
       <c r="B7" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 18680-2024 artfynd.xlsx
+++ b/artfynd/A 18680-2024 artfynd.xlsx
@@ -1137,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121152794</v>
+        <v>121152787</v>
       </c>
       <c r="B6" t="n">
-        <v>97055</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,30 +1149,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542863</v>
+        <v>542650</v>
       </c>
       <c r="R6" t="n">
-        <v>6853500</v>
+        <v>6853570</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121152787</v>
+        <v>121152794</v>
       </c>
       <c r="B7" t="n">
-        <v>98095</v>
+        <v>97058</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,30 +1260,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542650</v>
+        <v>542863</v>
       </c>
       <c r="R7" t="n">
-        <v>6853570</v>
+        <v>6853500</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
